--- a/kits/cra-readiness/samples/mossbyte-sprout-s1/deliverables/vulnerability-report.xlsx
+++ b/kits/cra-readiness/samples/mossbyte-sprout-s1/deliverables/vulnerability-report.xlsx
@@ -1186,7 +1186,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr"/>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-qwcr-r2fm-qrc7</t>
@@ -1259,7 +1263,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-w3h3-4rj7-4ph4</t>
@@ -1332,7 +1340,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr"/>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-hc5x-x2vx-497g</t>
@@ -1409,7 +1421,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-9wv6-86v2-598j</t>
@@ -1486,7 +1502,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-rhx6-c78j-4q9w</t>
@@ -1563,7 +1583,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-2g68-c3qc-8985</t>
@@ -1636,7 +1660,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr"/>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-rv95-896h-c2vc</t>
@@ -1702,7 +1730,7 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>python-dotenv: Symlink following in setkey allows arbitrary file overwrite via cross-device rename fallback</t>
+          <t>python-dotenv: Symlink following in set_key allows arbitrary file overwrite via cross-device rename fallback</t>
         </is>
       </c>
       <c r="K9" s="6" t="n">
@@ -1713,7 +1741,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-mf9w-mj56-hr94</t>
@@ -1790,7 +1822,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-6rw7-vpxm-498p</t>
@@ -1867,7 +1903,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-4mjr-xmp4-gh2g</t>
@@ -1940,7 +1980,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr"/>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-9wx4-h78v-vm56</t>
@@ -2013,7 +2057,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-9hjg-9r4m-mvj7</t>
@@ -2075,7 +2123,7 @@
       <c r="I14" s="6" t="inlineStr"/>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Requests has Insecure Temp File Reuse in its extractzippedpaths() utility function</t>
+          <t>Requests has Insecure Temp File Reuse in its extract_zipped_paths() utility function</t>
         </is>
       </c>
       <c r="K14" s="6" t="n">
@@ -2086,7 +2134,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-gc5v-m9x4-r6x2</t>
@@ -2152,7 +2204,7 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Werkzeug safejoin not safe on Windows</t>
+          <t>Werkzeug safe_join not safe on Windows</t>
         </is>
       </c>
       <c r="K15" s="6" t="n"/>
@@ -2161,7 +2213,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-f9vj-2wh5-fj8j</t>
@@ -2238,7 +2294,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-q34m-jh98-gwm2</t>
@@ -2304,7 +2364,7 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Werkzeug safejoin() allows Windows special device names</t>
+          <t>Werkzeug safe_join() allows Windows special device names</t>
         </is>
       </c>
       <c r="K17" s="6" t="n"/>
@@ -2313,7 +2373,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-hgf8-39gv-g3f2</t>
@@ -2379,7 +2443,7 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Werkzeug safejoin() allows Windows special device names</t>
+          <t>Werkzeug safe_join() allows Windows special device names</t>
         </is>
       </c>
       <c r="K18" s="6" t="n"/>
@@ -2388,7 +2452,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-g6x2-hccm-hh4m</t>
@@ -2454,7 +2522,7 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Werkzeug safejoin() allows Windows special device names with compound extensions</t>
+          <t>Werkzeug safe_join() allows Windows special device names with compound extensions</t>
         </is>
       </c>
       <c r="K19" s="6" t="n">
@@ -2465,7 +2533,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-87hc-h4r5-73f7</t>
@@ -2531,7 +2603,7 @@
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>Werkzeug safejoin() allows Windows special device names</t>
+          <t>Werkzeug safe_join() allows Windows special device names</t>
         </is>
       </c>
       <c r="K20" s="6" t="n"/>
@@ -2540,7 +2612,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-29vq-49wr-vm6x</t>
@@ -2617,7 +2693,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-v422-hmwv-36x6</t>
@@ -2692,7 +2772,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-pxg6-pf52-xh8x</t>
@@ -2765,7 +2849,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-qw6h-vgh9-j6wx</t>
@@ -2836,7 +2924,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-68rp-wp8r-4726</t>
@@ -2913,7 +3005,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-w7fw-mjwx-w883</t>
@@ -2990,7 +3086,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M26" s="6" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-m6fv-jmcg-4jfg</t>
@@ -3067,7 +3167,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>First check</t>
+        </is>
+      </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
           <t>https://github.com/advisories/GHSA-cm22-4g7w-348p</t>
@@ -3465,7 +3569,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>55f9747c1095e75a26193b5143f5475fadeeb951a6d02ef95ac9fa5532f7cf8c</t>
+          <t>4f5ab08eeaf59d6b6bf892c7c7d87284c258d0f53277fc0e528fac63fc85e3c2</t>
         </is>
       </c>
     </row>

--- a/kits/cra-readiness/samples/mossbyte-sprout-s1/deliverables/vulnerability-report.xlsx
+++ b/kits/cra-readiness/samples/mossbyte-sprout-s1/deliverables/vulnerability-report.xlsx
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>4f5ab08eeaf59d6b6bf892c7c7d87284c258d0f53277fc0e528fac63fc85e3c2</t>
+          <t>bd8a853f91a04f9e508902a870f70683058e7fd9fa4c8ba0b6fcec0acaf0956e</t>
         </is>
       </c>
     </row>
